--- a/Analysis/cluster_bootstrap_ci.xlsx
+++ b/Analysis/cluster_bootstrap_ci.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1112,31 +1112,31 @@
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3668</v>
+        <v>0.2314</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3175</v>
+        <v>0.2224</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4166</v>
+        <v>0.2409</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0185</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3471</v>
+        <v>0.2296</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3948</v>
+        <v>0.2336</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0477</v>
+        <v>0.0039</v>
       </c>
       <c r="M14" t="n">
-        <v>2.08</v>
+        <v>4.72</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0309</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="15">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1162,31 +1162,31 @@
         <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3621</v>
+        <v>0.219</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3005</v>
+        <v>0.2067</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4256</v>
+        <v>0.2319</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1251</v>
+        <v>0.0252</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3508</v>
+        <v>0.2176</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3744</v>
+        <v>0.2202</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0236</v>
+        <v>0.0026</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0148</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="16">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1212,31 +1212,31 @@
         <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3333</v>
+        <v>0.2411</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2903</v>
+        <v>0.2299</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3774</v>
+        <v>0.2526</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0872</v>
+        <v>0.0226</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3149</v>
+        <v>0.2396</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3518</v>
+        <v>0.2425</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0369</v>
+        <v>0.0029</v>
       </c>
       <c r="M16" t="n">
-        <v>2.36</v>
+        <v>7.79</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0241</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="17">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1262,31 +1262,31 @@
         <v>5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3001</v>
+        <v>0.2349</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2595</v>
+        <v>0.2248</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3419</v>
+        <v>0.2452</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0824</v>
+        <v>0.0204</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2772</v>
+        <v>0.2336</v>
       </c>
       <c r="K17" t="n">
-        <v>0.323</v>
+        <v>0.2364</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0458</v>
+        <v>0.0028</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8</v>
+        <v>7.29</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0296</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="18">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1312,31 +1312,31 @@
         <v>5</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5354</v>
+        <v>0.1677</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4831</v>
+        <v>0.1554</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5856</v>
+        <v>0.1809</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1026</v>
+        <v>0.0255</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5097</v>
+        <v>0.1671</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.1682</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0513</v>
+        <v>0.0011</v>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>23.97</v>
       </c>
       <c r="N18" t="n">
-        <v>0.033</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="19">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1362,31 +1362,31 @@
         <v>5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4871</v>
+        <v>0.1584</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4225</v>
+        <v>0.1461</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5526</v>
+        <v>0.1711</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1301</v>
+        <v>0.025</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4716</v>
+        <v>0.1575</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5026</v>
+        <v>0.1592</v>
       </c>
       <c r="L19" t="n">
-        <v>0.031</v>
+        <v>0.0016</v>
       </c>
       <c r="M19" t="n">
-        <v>4.19</v>
+        <v>15.35</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0199</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="20">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1412,31 +1412,31 @@
         <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4738</v>
+        <v>0.169</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4215</v>
+        <v>0.1577</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5262</v>
+        <v>0.1809</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1046</v>
+        <v>0.0232</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4564</v>
+        <v>0.1673</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4882</v>
+        <v>0.1708</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0318</v>
+        <v>0.0035</v>
       </c>
       <c r="M20" t="n">
-        <v>3.29</v>
+        <v>6.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0207</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="21">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1462,31 +1462,31 @@
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4656</v>
+        <v>0.1935</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4215</v>
+        <v>0.1819</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5087</v>
+        <v>0.2055</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0872</v>
+        <v>0.0236</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4533</v>
+        <v>0.1908</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4779</v>
+        <v>0.196</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0246</v>
+        <v>0.0053</v>
       </c>
       <c r="M21" t="n">
-        <v>3.54</v>
+        <v>4.49</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0156</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1512,31 +1512,31 @@
         <v>5</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9076</v>
+        <v>0.0448</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8694</v>
+        <v>0.0396</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9415</v>
+        <v>0.0506</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0721</v>
+        <v>0.011</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9003</v>
+        <v>0.0415</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9159</v>
+        <v>0.0476</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0156</v>
+        <v>0.006</v>
       </c>
       <c r="M22" t="n">
-        <v>4.62</v>
+        <v>1.83</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0097</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="23">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1562,31 +1562,31 @@
         <v>5</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9313</v>
+        <v>0.0477</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8933</v>
+        <v>0.0411</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9641</v>
+        <v>0.0547</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0708</v>
+        <v>0.0136</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9292</v>
+        <v>0.0472</v>
       </c>
       <c r="K23" t="n">
-        <v>0.9333</v>
+        <v>0.0483</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0041</v>
+        <v>0.0011</v>
       </c>
       <c r="M23" t="n">
-        <v>17.25</v>
+        <v>12.28</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0028</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="24">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1612,31 +1612,31 @@
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9173</v>
+        <v>0.0519</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8828</v>
+        <v>0.0461</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9479</v>
+        <v>0.0581</v>
       </c>
       <c r="I24" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.012</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9131</v>
+        <v>0.051</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9234</v>
+        <v>0.0532</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0104</v>
+        <v>0.0022</v>
       </c>
       <c r="M24" t="n">
-        <v>6.29</v>
+        <v>5.57</v>
       </c>
       <c r="N24" t="n">
-        <v>0.007</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1662,31 +1662,31 @@
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8972</v>
+        <v>0.0718</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8571</v>
+        <v>0.0612</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9342</v>
+        <v>0.0832</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0771</v>
+        <v>0.0219</v>
       </c>
       <c r="J25" t="n">
-        <v>0.89</v>
+        <v>0.0702</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9074</v>
+        <v>0.0731</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0174</v>
+        <v>0.0028</v>
       </c>
       <c r="M25" t="n">
-        <v>4.43</v>
+        <v>7.81</v>
       </c>
       <c r="N25" t="n">
-        <v>0.0119</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="26">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1712,31 +1712,31 @@
         <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7221</v>
+        <v>0.3668</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.3175</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7683</v>
+        <v>0.4166</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0954</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7104</v>
+        <v>0.3471</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7378</v>
+        <v>0.3948</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0274</v>
+        <v>0.0477</v>
       </c>
       <c r="M26" t="n">
-        <v>3.49</v>
+        <v>2.08</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0178</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="27">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1762,31 +1762,31 @@
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6974</v>
+        <v>0.3621</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6359</v>
+        <v>0.3005</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7559</v>
+        <v>0.4256</v>
       </c>
       <c r="I27" t="n">
-        <v>0.12</v>
+        <v>0.1251</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6841</v>
+        <v>0.3508</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7087</v>
+        <v>0.3744</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0246</v>
+        <v>0.0236</v>
       </c>
       <c r="M27" t="n">
-        <v>4.87</v>
+        <v>5.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0162</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="28">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1812,31 +1812,31 @@
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6646</v>
+        <v>0.3333</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.2903</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7077</v>
+        <v>0.3774</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0882</v>
+        <v>0.0872</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6451</v>
+        <v>0.3149</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6862</v>
+        <v>0.3518</v>
       </c>
       <c r="L28" t="n">
-        <v>0.041</v>
+        <v>0.0369</v>
       </c>
       <c r="M28" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0263</v>
+        <v>0.0241</v>
       </c>
     </row>
     <row r="29">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1862,31 +1862,31 @@
         <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6773</v>
+        <v>0.3001</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6385</v>
+        <v>0.2595</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7161</v>
+        <v>0.3419</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0776</v>
+        <v>0.0824</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6571</v>
+        <v>0.2772</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6958</v>
+        <v>0.323</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0387</v>
+        <v>0.0458</v>
       </c>
       <c r="M29" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.025</v>
+        <v>0.0296</v>
       </c>
     </row>
     <row r="30">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1912,31 +1912,31 @@
         <v>5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8113</v>
+        <v>0.5354</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7703</v>
+        <v>0.4831</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.5856</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08</v>
+        <v>0.1026</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.5097</v>
       </c>
       <c r="K30" t="n">
-        <v>0.8318</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>0.04</v>
+        <v>0.0513</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0239</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="31">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1962,31 +1962,31 @@
         <v>5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7958</v>
+        <v>0.4871</v>
       </c>
       <c r="G31" t="n">
-        <v>0.741</v>
+        <v>0.4225</v>
       </c>
       <c r="H31" t="n">
-        <v>0.847</v>
+        <v>0.5526</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1061</v>
+        <v>0.1301</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7927</v>
+        <v>0.4716</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8004</v>
+        <v>0.5026</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0077</v>
+        <v>0.031</v>
       </c>
       <c r="M31" t="n">
-        <v>13.86</v>
+        <v>4.19</v>
       </c>
       <c r="N31" t="n">
-        <v>0.005</v>
+        <v>0.0199</v>
       </c>
     </row>
     <row r="32">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -2012,31 +2012,31 @@
         <v>5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7651</v>
+        <v>0.4738</v>
       </c>
       <c r="G32" t="n">
-        <v>0.719</v>
+        <v>0.4215</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8092</v>
+        <v>0.5262</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.1046</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7436</v>
+        <v>0.4564</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7856</v>
+        <v>0.4882</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0421</v>
+        <v>0.0318</v>
       </c>
       <c r="M32" t="n">
-        <v>2.15</v>
+        <v>3.29</v>
       </c>
       <c r="N32" t="n">
-        <v>0.027</v>
+        <v>0.0207</v>
       </c>
     </row>
     <row r="33">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2062,31 +2062,31 @@
         <v>5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7805</v>
+        <v>0.4656</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7456</v>
+        <v>0.4215</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8144</v>
+        <v>0.5087</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0687</v>
+        <v>0.0872</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7579</v>
+        <v>0.4533</v>
       </c>
       <c r="K33" t="n">
-        <v>0.8051</v>
+        <v>0.4779</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0472</v>
+        <v>0.0246</v>
       </c>
       <c r="M33" t="n">
-        <v>1.46</v>
+        <v>3.54</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0302</v>
+        <v>0.0156</v>
       </c>
     </row>
     <row r="34">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2112,31 +2112,31 @@
         <v>5</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9774</v>
+        <v>0.9076</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9567</v>
+        <v>0.8694</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9949</v>
+        <v>0.9415</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0381</v>
+        <v>0.0721</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9003</v>
       </c>
       <c r="K34" t="n">
-        <v>0.9815</v>
+        <v>0.9159</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0072</v>
+        <v>0.0156</v>
       </c>
       <c r="M34" t="n">
-        <v>5.27</v>
+        <v>4.62</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0046</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="35">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2162,29 +2162,31 @@
         <v>5</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9846</v>
+        <v>0.9313</v>
       </c>
       <c r="G35" t="n">
+        <v>0.8933</v>
+      </c>
+      <c r="H35" t="n">
         <v>0.9641</v>
       </c>
-      <c r="H35" t="n">
-        <v>1</v>
-      </c>
       <c r="I35" t="n">
-        <v>0.0359</v>
+        <v>0.0708</v>
       </c>
       <c r="J35" t="n">
-        <v>0.9846</v>
+        <v>0.9292</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9846</v>
+        <v>0.9333</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr"/>
+        <v>0.0041</v>
+      </c>
+      <c r="M35" t="n">
+        <v>17.25</v>
+      </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="36">
@@ -2200,7 +2202,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2210,31 +2212,31 @@
         <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9813</v>
+        <v>0.9173</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9647</v>
+        <v>0.8828</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9942</v>
+        <v>0.9479</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0294</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9752</v>
+        <v>0.9131</v>
       </c>
       <c r="K36" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9234</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0132</v>
+        <v>0.0104</v>
       </c>
       <c r="M36" t="n">
-        <v>2.24</v>
+        <v>6.29</v>
       </c>
       <c r="N36" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="37">
@@ -2250,40 +2252,638 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>195</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8972</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.0771</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.9074</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.0119</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A_D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>top2_accuracy</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>195</v>
-      </c>
-      <c r="E37" t="n">
-        <v>5</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="D38" t="n">
+        <v>195</v>
+      </c>
+      <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.7221</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.6729000000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.7683</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0954</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.7104</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.7378</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.0178</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A_D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>195</v>
+      </c>
+      <c r="E39" t="n">
+        <v>5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.6974</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.6359</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7559</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6841</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.7087</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.0246</v>
+      </c>
+      <c r="M39" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.0162</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A_D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>195</v>
+      </c>
+      <c r="E40" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.6646</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6195000000000001</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.7077</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0882</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6451</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.6862</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.0263</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A_D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>195</v>
+      </c>
+      <c r="E41" t="n">
+        <v>5</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6773</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.6385</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7161</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.0776</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.6571</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.0387</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.025</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A_E</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>195</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.8113</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.7703</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8502999999999999</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.7917999999999999</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.8318</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.0239</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A_E</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>195</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7958</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1061</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.7927</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.8004</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="M43" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A_E</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>195</v>
+      </c>
+      <c r="E44" t="n">
+        <v>5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.7651</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.8092</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.09030000000000001</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.7436</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.7856</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.027</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A_E</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>195</v>
+      </c>
+      <c r="E45" t="n">
+        <v>5</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.7805</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.7456</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.8144</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.0687</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.7579</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.0472</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.0302</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A_H</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>195</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9774</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9567</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9743000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.9815</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="M46" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.0046</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A_H</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>195</v>
+      </c>
+      <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.9641</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9846</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A_H</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>194</v>
+      </c>
+      <c r="E48" t="n">
+        <v>5</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.9813</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.9647</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.9942</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9752</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9883999999999999</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A_H</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>195</v>
+      </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+      <c r="F49" t="n">
         <v>0.9692</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G49" t="n">
         <v>0.9455</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H49" t="n">
         <v>0.9887</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I49" t="n">
         <v>0.0432</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J49" t="n">
         <v>0.9631</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K49" t="n">
         <v>0.9752999999999999</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L49" t="n">
         <v>0.0122</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M49" t="n">
         <v>3.54</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N49" t="n">
         <v>0.0072</v>
       </c>
     </row>
@@ -2298,7 +2898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2388,20 +2988,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1686</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1012</v>
+        <v>-0.07480000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2338</v>
+        <v>-0.0523</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -2420,20 +3020,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>195</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0892</v>
+        <v>0.1686</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0315</v>
+        <v>0.1012</v>
       </c>
       <c r="G4" t="n">
-        <v>0.147</v>
+        <v>0.2338</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -2447,25 +3047,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5907</v>
+        <v>0.0892</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5108</v>
+        <v>0.0315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6715</v>
+        <v>0.147</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -2484,20 +3084,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>195</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3722</v>
+        <v>0.5907</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3126</v>
+        <v>0.5108</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4344</v>
+        <v>0.6715</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -2516,20 +3116,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>195</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1661</v>
+        <v>-0.1229</v>
       </c>
       <c r="F7" t="n">
-        <v>0.121</v>
+        <v>-0.1362</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2123</v>
+        <v>-0.1102</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -2543,25 +3143,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>195</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7533</v>
+        <v>0.3722</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6662</v>
+        <v>0.3126</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8418</v>
+        <v>0.4344</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -2575,25 +3175,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>195</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.1661</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4765</v>
+        <v>0.121</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6037</v>
+        <v>0.2123</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -2612,20 +3212,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>195</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2553</v>
+        <v>0.7533</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2033</v>
+        <v>0.6662</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3091</v>
+        <v>0.8418</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -2634,30 +3234,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>195</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1338</v>
+        <v>-0.1866</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0544</v>
+        <v>-0.1971</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2155</v>
+        <v>-0.1761</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -2666,12 +3266,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2683,13 +3283,13 @@
         <v>195</v>
       </c>
       <c r="E12" t="n">
-        <v>0.125</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0524</v>
+        <v>0.4765</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1996</v>
+        <v>0.6037</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -2698,12 +3298,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>gemini</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2715,13 +3315,13 @@
         <v>195</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0984</v>
+        <v>0.2553</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0515</v>
+        <v>0.2033</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1478</v>
+        <v>0.3091</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -2735,7 +3335,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2747,13 +3347,13 @@
         <v>195</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6135</v>
+        <v>0.1338</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5143</v>
+        <v>0.0544</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7143</v>
+        <v>0.2155</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -2767,25 +3367,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>195</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4442</v>
+        <v>-0.0607</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3704</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5165</v>
+        <v>-0.0501</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -2799,25 +3399,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>195</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1888</v>
+        <v>0.125</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1334</v>
+        <v>0.0524</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2477</v>
+        <v>0.1996</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -2831,25 +3431,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>195</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7474</v>
+        <v>0.0984</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6544</v>
+        <v>0.0515</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8417</v>
+        <v>0.1478</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -2863,25 +3463,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>195</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5692</v>
+        <v>0.6135</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5026</v>
+        <v>0.5143</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6349</v>
+        <v>0.7143</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -2895,25 +3495,25 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>195</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2872</v>
+        <v>-0.1107</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2277</v>
+        <v>-0.1245</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3497</v>
+        <v>-0.0975</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -2922,30 +3522,30 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>195</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2318</v>
+        <v>0.4442</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1525</v>
+        <v>0.3704</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3104</v>
+        <v>0.5165</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -2954,30 +3554,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>195</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1405</v>
+        <v>0.1888</v>
       </c>
       <c r="F21" t="n">
-        <v>0.08</v>
+        <v>0.1334</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1979</v>
+        <v>0.2477</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -2986,30 +3586,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>195</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1005</v>
+        <v>0.7474</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0472</v>
+        <v>0.6544</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1518</v>
+        <v>0.8417</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -3018,30 +3618,30 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E23" t="n">
-        <v>0.628</v>
+        <v>-0.1713</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5474</v>
+        <v>-0.1848</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7105</v>
+        <v>-0.1584</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -3050,12 +3650,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3064,16 +3664,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4451</v>
+        <v>0.5692</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3849</v>
+        <v>0.5026</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5038</v>
+        <v>0.6349</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -3082,12 +3682,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>gptoss</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3096,16 +3696,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2173</v>
+        <v>0.2872</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1713</v>
+        <v>0.2277</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2662</v>
+        <v>0.3497</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -3119,7 +3719,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3128,16 +3728,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8569</v>
+        <v>0.2318</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7844</v>
+        <v>0.1525</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9283</v>
+        <v>0.3104</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -3151,25 +3751,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5843</v>
+        <v>-0.0721</v>
       </c>
       <c r="F27" t="n">
-        <v>0.532</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.636</v>
+        <v>-0.0597</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -3183,25 +3783,25 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A_H - A_D</t>
+          <t>A_E - A_D</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3173</v>
+        <v>0.1405</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2737</v>
+        <v>0.08</v>
       </c>
       <c r="G28" t="n">
-        <v>0.362</v>
+        <v>0.1979</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -3210,7 +3810,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3220,20 +3820,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>195</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1982</v>
+        <v>0.1005</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1062</v>
+        <v>0.0472</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2889</v>
+        <v>0.1518</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -3242,30 +3842,30 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1655</v>
+        <v>0.628</v>
       </c>
       <c r="F30" t="n">
-        <v>0.1018</v>
+        <v>0.5474</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2284</v>
+        <v>0.7105</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -3274,30 +3874,30 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A_E - A_D</t>
+          <t>A_H - A_E</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1032</v>
+        <v>-0.1177</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0462</v>
+        <v>-0.1302</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1591</v>
+        <v>-0.106</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -3306,7 +3906,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3316,20 +3916,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>top1_accuracy</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6719000000000001</v>
+        <v>0.4451</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5985</v>
+        <v>0.3849</v>
       </c>
       <c r="G32" t="n">
-        <v>0.7423</v>
+        <v>0.5038</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -3338,7 +3938,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3348,20 +3948,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>top1_accuracy</t>
+          <t>top2_accuracy</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4316</v>
+        <v>0.2173</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3741</v>
+        <v>0.1713</v>
       </c>
       <c r="G33" t="n">
-        <v>0.4882</v>
+        <v>0.2662</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -3370,30 +3970,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A_H - A_E</t>
+          <t>A_H - A_D</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>top2_accuracy</t>
+          <t>kendall_tau</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1887</v>
+        <v>0.8569</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1487</v>
+        <v>0.7844</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2276</v>
+        <v>0.9283</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -3402,7 +4002,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3412,20 +4012,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>kendall_tau</t>
+          <t>overall_mae</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8701</v>
+        <v>-0.1894</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7973</v>
+        <v>-0.2023</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9405</v>
+        <v>-0.1763</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -3434,7 +4034,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>qwen</t>
+          <t>gptoss</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3448,16 +4048,16 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5971</v>
+        <v>0.5843</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5419</v>
+        <v>0.532</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6505</v>
+        <v>0.636</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -3466,32 +4066,416 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A_H - A_D</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>194</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.2737</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>qwen</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A_E - A_D</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>195</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A_E - A_D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>overall_mae</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>195</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.0413</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.0521</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-0.0305</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A_E - A_D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>195</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.1018</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.2284</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A_E - A_D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>195</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1032</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1591</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A_H - A_E</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>195</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6719000000000001</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.5985</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.7423</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A_H - A_E</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>overall_mae</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>195</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-0.1217</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-0.138</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-0.1053</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A_H - A_E</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>195</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.4882</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A_H - A_E</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>195</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1887</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.1487</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.2276</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>A_H - A_D</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>195</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A_H - A_D</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>overall_mae</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>195</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.1631</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.1748</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-0.1513</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A_H - A_D</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>195</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.5971</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.5419</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6505</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A_H - A_D</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
         <is>
           <t>top2_accuracy</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>195</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D49" t="n">
+        <v>195</v>
+      </c>
+      <c r="E49" t="n">
         <v>0.2919</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F49" t="n">
         <v>0.2462</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G49" t="n">
         <v>0.337</v>
       </c>
-      <c r="H37" t="b">
+      <c r="H49" t="b">
         <v>1</v>
       </c>
     </row>
